--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
         <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -829,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M65" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="M67" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N67" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,16 +8439,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="M83" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14990,10 +14990,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="M131" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N131" t="n">
-        <v>1.89</v>
+        <v>4.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.19</v>
+        <v>3.95</v>
       </c>
       <c r="M143" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N143" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19104,10 +19104,10 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="M157" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N157" t="n">
         <v>3</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M162" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N162" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M177" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N177" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="M178" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G184" t="n">

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI187"/>
+  <dimension ref="A1:AI189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.29166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.3125</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.3125</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.32291666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46004.29166666666</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46004.3125</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46004.3125</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Perth Glory FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46004.32291666666</v>
+        <v>46004.35416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.35416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46004.35416666666</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="21">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46004.375</v>
+        <v>46004.39583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46004.375</v>
+        <v>46004.39583333334</v>
       </c>
     </row>
     <row r="25">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46004.39583333334</v>
+        <v>46004.41666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46004.39583333334</v>
+        <v>46004.41666666666</v>
       </c>
     </row>
     <row r="33">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46004.41666666666</v>
+        <v>46004.4375</v>
       </c>
     </row>
     <row r="44">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46004.4375</v>
+        <v>46004.45833333334</v>
       </c>
     </row>
     <row r="51">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46004.45833333334</v>
+        <v>46004.47916666666</v>
       </c>
     </row>
     <row r="64">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8445,10 +8445,10 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>46004.47916666666</v>
+        <v>46004.5</v>
       </c>
     </row>
     <row r="68">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N83" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="M97" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46004.5</v>
+        <v>46004.51041666666</v>
       </c>
     </row>
     <row r="116">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46004.51041666666</v>
+        <v>46004.52083333334</v>
       </c>
     </row>
     <row r="119">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15109,10 +15109,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="M140" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N140" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M142" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N142" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>46004.59375</v>
+        <v>46004.58333333334</v>
       </c>
     </row>
     <row r="158">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46004.60416666666</v>
+        <v>46004.59375</v>
       </c>
     </row>
     <row r="159">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="M162" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N162" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46004.61458333334</v>
+        <v>46004.60416666666</v>
       </c>
     </row>
     <row r="163">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="M163" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="N163" t="n">
-        <v>1.23</v>
+        <v>5.8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD163" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>46004.625</v>
+        <v>46004.60416666666</v>
       </c>
     </row>
     <row r="164">
@@ -19896,12 +19896,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20006,7 +20006,7 @@
         <v>0</v>
       </c>
       <c r="AI164" s="3" t="n">
-        <v>46004.625</v>
+        <v>46004.61458333334</v>
       </c>
     </row>
     <row r="165">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="M167" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="N167" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,16 +20339,16 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD167" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE167" t="n">
         <v>0</v>
@@ -20372,12 +20372,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20482,7 +20482,7 @@
         <v>0</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>46004.64583333334</v>
+        <v>46004.625</v>
       </c>
     </row>
     <row r="169">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20601,7 +20601,7 @@
         <v>0</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>46004.64583333334</v>
+        <v>46004.625</v>
       </c>
     </row>
     <row r="170">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20720,7 +20720,7 @@
         <v>0</v>
       </c>
       <c r="AI170" s="3" t="n">
-        <v>46004.66666666666</v>
+        <v>46004.64583333334</v>
       </c>
     </row>
     <row r="171">
@@ -20729,12 +20729,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20839,7 +20839,7 @@
         <v>0</v>
       </c>
       <c r="AI171" s="3" t="n">
-        <v>46004.66666666666</v>
+        <v>46004.64583333334</v>
       </c>
     </row>
     <row r="172">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21205,12 +21205,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21315,7 +21315,7 @@
         <v>0</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>46004.6875</v>
+        <v>46004.66666666666</v>
       </c>
     </row>
     <row r="176">
@@ -21324,12 +21324,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>46004.6875</v>
+        <v>46004.66666666666</v>
       </c>
     </row>
     <row r="177">
@@ -21443,12 +21443,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21553,7 +21553,7 @@
         <v>0</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>46004.69791666666</v>
+        <v>46004.6875</v>
       </c>
     </row>
     <row r="178">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>46004.69791666666</v>
+        <v>46004.6875</v>
       </c>
     </row>
     <row r="179">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>46004.70833333334</v>
+        <v>46004.69791666666</v>
       </c>
     </row>
     <row r="180">
@@ -21800,12 +21800,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="M180" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="N180" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21910,7 +21910,7 @@
         <v>0</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>46004.70833333334</v>
+        <v>46004.69791666666</v>
       </c>
     </row>
     <row r="181">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22395,12 +22395,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22505,7 +22505,7 @@
         <v>0</v>
       </c>
       <c r="AI185" s="3" t="n">
-        <v>46004.71180555555</v>
+        <v>46004.70833333334</v>
       </c>
     </row>
     <row r="186">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22624,7 +22624,7 @@
         <v>0</v>
       </c>
       <c r="AI186" s="3" t="n">
-        <v>46004.72916666666</v>
+        <v>46004.70833333334</v>
       </c>
     </row>
     <row r="187">
@@ -22633,116 +22633,354 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>France Ligue 1</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M187" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" t="n">
+        <v>0</v>
+      </c>
+      <c r="X187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="3" t="n">
+        <v>46004.71180555555</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI188" s="3" t="n">
+        <v>46004.72916666666</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Australia A-League</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>Wellington Phoenix</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Newcastle Jets FC</t>
         </is>
       </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" t="inlineStr">
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L187" t="n">
+      <c r="L189" t="n">
         <v>2.37</v>
       </c>
-      <c r="M187" t="n">
+      <c r="M189" t="n">
         <v>3.75</v>
       </c>
-      <c r="N187" t="n">
+      <c r="N189" t="n">
         <v>2.55</v>
       </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="n">
-        <v>0</v>
-      </c>
-      <c r="T187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" t="n">
-        <v>0</v>
-      </c>
-      <c r="W187" t="n">
-        <v>0</v>
-      </c>
-      <c r="X187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC187" t="n">
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" t="n">
+        <v>0</v>
+      </c>
+      <c r="X189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC189" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD187" t="n">
+      <c r="AD189" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI187" s="3" t="n">
+      <c r="AE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI189" s="3" t="n">
         <v>46004.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N60" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N64" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N66" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8326,10 +8326,10 @@
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N96" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB96" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>1.55</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14871,10 +14871,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15109,10 +15109,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="M133" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N133" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="M163" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N163" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,16 +19863,16 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC163" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20345,10 +20345,10 @@
         <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD167" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="M169" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="N169" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,16 +20577,16 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD169" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G186" t="n">

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M64" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8326,10 +8326,10 @@
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M101" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N101" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.83</v>
+        <v>3.95</v>
       </c>
       <c r="M128" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="M182" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N182" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N64" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="M65" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,16 +8320,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="M101" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>4.7</v>
+        <v>1.82</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,16 +12961,16 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="M125" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N125" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N130" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="M169" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="N169" t="n">
-        <v>1.23</v>
+        <v>3.45</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,16 +20577,16 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N179" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M180" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N180" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G186" t="n">

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="M18" t="n">
         <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="M64" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,16 +12961,16 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14871,10 +14871,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14990,10 +14990,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N126" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="M161" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,16 +19625,16 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M179" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M180" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N180" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G186" t="n">

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="M64" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,16 +8320,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="M94" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>4.7</v>
+        <v>1.91</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="M95" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N95" t="n">
-        <v>1.82</v>
+        <v>3.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="M96" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>3.95</v>
+        <v>2.85</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14990,10 +14990,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="M127" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB127" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M129" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N129" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19631,10 +19631,10 @@
         <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20345,10 +20345,10 @@
         <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD167" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N179" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M180" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N180" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G186" t="n">

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="M66" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,16 +8320,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M95" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="N95" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,16 +11771,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M98" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.07</v>
+        <v>4.1</v>
       </c>
       <c r="M101" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>3.35</v>
+        <v>1.82</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="M107" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N107" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14514,10 +14514,10 @@
         <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
         <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N130" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="M133" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N133" t="n">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="M159" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20345,10 +20345,10 @@
         <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD167" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20464,10 +20464,10 @@
         <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD168" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M179" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M180" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N180" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N60" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="M65" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,16 +8320,16 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,16 +11771,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N101" t="n">
-        <v>1.82</v>
+        <v>4.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14514,10 +14514,10 @@
         <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M132" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N132" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="M159" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N159" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N179" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M180" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N180" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="M184" t="n">
-        <v>3.65</v>
+        <v>6.7</v>
       </c>
       <c r="N184" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB184" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI189"/>
+  <dimension ref="A1:AI186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.3125</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46004.25</v>
+        <v>46004.3125</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sydney FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46004.29166666666</v>
+        <v>46004.32291666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46004.3125</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46004.3125</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Perth Glory FC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sydney FC</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46004.32291666666</v>
+        <v>46004.33333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.35416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.35416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46004.33333333334</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46004.35416666666</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46004.35416666666</v>
+        <v>46004.375</v>
       </c>
     </row>
     <row r="17">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46004.375</v>
+        <v>46004.39583333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46004.375</v>
+        <v>46004.39583333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46004.375</v>
+        <v>46004.39583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46004.39583333334</v>
+        <v>46004.41666666666</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46004.39583333334</v>
+        <v>46004.41666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46004.39583333334</v>
+        <v>46004.41666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46004.41666666666</v>
+        <v>46004.4375</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46004.41666666666</v>
+        <v>46004.4375</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46004.41666666666</v>
+        <v>46004.4375</v>
       </c>
     </row>
     <row r="43">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46004.4375</v>
+        <v>46004.45833333334</v>
       </c>
     </row>
     <row r="48">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46004.4375</v>
+        <v>46004.45833333334</v>
       </c>
     </row>
     <row r="49">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46004.4375</v>
+        <v>46004.45833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>46004.45833333334</v>
+        <v>46004.47916666666</v>
       </c>
     </row>
     <row r="61">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7731,10 +7731,10 @@
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3" t="n">
-        <v>46004.45833333334</v>
+        <v>46004.47916666666</v>
       </c>
     </row>
     <row r="62">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46004.45833333334</v>
+        <v>46004.47916666666</v>
       </c>
     </row>
     <row r="63">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46004.47916666666</v>
+        <v>46004.5</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46004.47916666666</v>
+        <v>46004.5</v>
       </c>
     </row>
     <row r="66">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8326,10 +8326,10 @@
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>46004.47916666666</v>
+        <v>46004.5</v>
       </c>
     </row>
     <row r="67">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="M92" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="M109" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N110" t="n">
-        <v>2.55</v>
+        <v>7.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46004.5</v>
+        <v>46004.51041666666</v>
       </c>
     </row>
     <row r="113">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46004.5</v>
+        <v>46004.51041666666</v>
       </c>
     </row>
     <row r="114">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M114" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46004.5</v>
+        <v>46004.51041666666</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46004.51041666666</v>
+        <v>46004.52083333334</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46004.51041666666</v>
+        <v>46004.52083333334</v>
       </c>
     </row>
     <row r="117">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46004.51041666666</v>
+        <v>46004.52083333334</v>
       </c>
     </row>
     <row r="118">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M119" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N119" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14752,10 +14752,10 @@
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46004.52083333334</v>
+        <v>46004.54166666666</v>
       </c>
     </row>
     <row r="122">
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="3" t="n">
-        <v>46004.52083333334</v>
+        <v>46004.54166666666</v>
       </c>
     </row>
     <row r="123">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46004.52083333334</v>
+        <v>46004.54166666666</v>
       </c>
     </row>
     <row r="124">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="M132" t="n">
         <v>3.35</v>
       </c>
       <c r="N132" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="3" t="n">
-        <v>46004.54166666666</v>
+        <v>46004.55208333334</v>
       </c>
     </row>
     <row r="142">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17388,7 +17388,7 @@
         <v>0</v>
       </c>
       <c r="AI142" s="3" t="n">
-        <v>46004.54166666666</v>
+        <v>46004.5625</v>
       </c>
     </row>
     <row r="143">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17507,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="3" t="n">
-        <v>46004.54166666666</v>
+        <v>46004.5625</v>
       </c>
     </row>
     <row r="144">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17626,7 +17626,7 @@
         <v>0</v>
       </c>
       <c r="AI144" s="3" t="n">
-        <v>46004.55208333334</v>
+        <v>46004.5625</v>
       </c>
     </row>
     <row r="145">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17745,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="AI145" s="3" t="n">
-        <v>46004.5625</v>
+        <v>46004.57291666666</v>
       </c>
     </row>
     <row r="146">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17864,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="AI146" s="3" t="n">
-        <v>46004.5625</v>
+        <v>46004.58333333334</v>
       </c>
     </row>
     <row r="147">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17983,7 +17983,7 @@
         <v>0</v>
       </c>
       <c r="AI147" s="3" t="n">
-        <v>46004.5625</v>
+        <v>46004.58333333334</v>
       </c>
     </row>
     <row r="148">
@@ -17992,12 +17992,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18102,7 +18102,7 @@
         <v>0</v>
       </c>
       <c r="AI148" s="3" t="n">
-        <v>46004.57291666666</v>
+        <v>46004.58333333334</v>
       </c>
     </row>
     <row r="149">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46004.58333333334</v>
+        <v>46004.59375</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46004.58333333334</v>
+        <v>46004.60416666666</v>
       </c>
     </row>
     <row r="157">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="3" t="n">
-        <v>46004.58333333334</v>
+        <v>46004.60416666666</v>
       </c>
     </row>
     <row r="158">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="M158" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="3" t="n">
-        <v>46004.59375</v>
+        <v>46004.60416666666</v>
       </c>
     </row>
     <row r="159">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="M159" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19649,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>46004.60416666666</v>
+        <v>46004.61458333334</v>
       </c>
     </row>
     <row r="162">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46004.60416666666</v>
+        <v>46004.625</v>
       </c>
     </row>
     <row r="163">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="3" t="n">
-        <v>46004.60416666666</v>
+        <v>46004.625</v>
       </c>
     </row>
     <row r="164">
@@ -19896,12 +19896,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M164" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N164" t="n">
-        <v>6.1</v>
+        <v>3.45</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20006,7 +20006,7 @@
         <v>0</v>
       </c>
       <c r="AI164" s="3" t="n">
-        <v>46004.61458333334</v>
+        <v>46004.625</v>
       </c>
     </row>
     <row r="165">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="M165" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="N165" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,16 +20101,16 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20253,12 +20253,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20363,7 +20363,7 @@
         <v>0</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>46004.625</v>
+        <v>46004.64583333334</v>
       </c>
     </row>
     <row r="168">
@@ -20372,12 +20372,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="M168" t="n">
-        <v>6.7</v>
+        <v>3.45</v>
       </c>
       <c r="N168" t="n">
-        <v>1.23</v>
+        <v>5.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,16 +20458,16 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD168" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE168" t="n">
         <v>0</v>
@@ -20482,7 +20482,7 @@
         <v>0</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>46004.625</v>
+        <v>46004.64583333334</v>
       </c>
     </row>
     <row r="169">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20601,7 +20601,7 @@
         <v>0</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>46004.625</v>
+        <v>46004.66666666666</v>
       </c>
     </row>
     <row r="170">
@@ -20610,12 +20610,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20720,7 +20720,7 @@
         <v>0</v>
       </c>
       <c r="AI170" s="3" t="n">
-        <v>46004.64583333334</v>
+        <v>46004.66666666666</v>
       </c>
     </row>
     <row r="171">
@@ -20729,12 +20729,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M171" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N171" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20839,7 +20839,7 @@
         <v>0</v>
       </c>
       <c r="AI171" s="3" t="n">
-        <v>46004.64583333334</v>
+        <v>46004.66666666666</v>
       </c>
     </row>
     <row r="172">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -21086,12 +21086,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.11</v>
+        <v>2.07</v>
       </c>
       <c r="M174" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="N174" t="n">
-        <v>20</v>
+        <v>3.15</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21178,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21196,7 +21196,7 @@
         <v>0</v>
       </c>
       <c r="AI174" s="3" t="n">
-        <v>46004.66666666666</v>
+        <v>46004.6875</v>
       </c>
     </row>
     <row r="175">
@@ -21205,12 +21205,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,10 +21291,10 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB175" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -21315,7 +21315,7 @@
         <v>0</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>46004.66666666666</v>
+        <v>46004.6875</v>
       </c>
     </row>
     <row r="176">
@@ -21324,12 +21324,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>46004.66666666666</v>
+        <v>46004.69791666666</v>
       </c>
     </row>
     <row r="177">
@@ -21443,12 +21443,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21553,7 +21553,7 @@
         <v>0</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>46004.6875</v>
+        <v>46004.69791666666</v>
       </c>
     </row>
     <row r="178">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="M178" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N178" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>46004.6875</v>
+        <v>46004.70833333334</v>
       </c>
     </row>
     <row r="179">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M179" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N179" t="n">
-        <v>5.1</v>
+        <v>1.84</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>46004.69791666666</v>
+        <v>46004.70833333334</v>
       </c>
     </row>
     <row r="180">
@@ -21800,12 +21800,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M180" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="N180" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21910,7 +21910,7 @@
         <v>0</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>46004.69791666666</v>
+        <v>46004.70833333334</v>
       </c>
     </row>
     <row r="181">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22276,12 +22276,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.19</v>
+        <v>2.35</v>
       </c>
       <c r="M184" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="N184" t="n">
-        <v>16</v>
+        <v>2.95</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB184" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
         <v>0</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>46004.70833333334</v>
+        <v>46004.71180555555</v>
       </c>
     </row>
     <row r="185">
@@ -22395,12 +22395,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22505,7 +22505,7 @@
         <v>0</v>
       </c>
       <c r="AI185" s="3" t="n">
-        <v>46004.70833333334</v>
+        <v>46004.72916666666</v>
       </c>
     </row>
     <row r="186">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22606,10 +22606,10 @@
         <v>0</v>
       </c>
       <c r="AC186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD186" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE186" t="n">
         <v>0</v>
@@ -22624,363 +22624,6 @@
         <v>0</v>
       </c>
       <c r="AI186" s="3" t="n">
-        <v>46004.70833333334</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>46004</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>France Ligue 1</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L187" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M187" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N187" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="n">
-        <v>0</v>
-      </c>
-      <c r="T187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" t="n">
-        <v>0</v>
-      </c>
-      <c r="W187" t="n">
-        <v>0</v>
-      </c>
-      <c r="X187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA187" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB187" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI187" s="3" t="n">
-        <v>46004.71180555555</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>46004</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Sporting CP</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>AVS</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L188" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" t="n">
-        <v>0</v>
-      </c>
-      <c r="U188" t="n">
-        <v>0</v>
-      </c>
-      <c r="V188" t="n">
-        <v>0</v>
-      </c>
-      <c r="W188" t="n">
-        <v>0</v>
-      </c>
-      <c r="X188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH188" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI188" s="3" t="n">
-        <v>46004.72916666666</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>46004</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Newcastle Jets FC</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L189" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="M189" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N189" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="n">
-        <v>0</v>
-      </c>
-      <c r="T189" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" t="n">
-        <v>0</v>
-      </c>
-      <c r="V189" t="n">
-        <v>0</v>
-      </c>
-      <c r="W189" t="n">
-        <v>0</v>
-      </c>
-      <c r="X189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC189" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD189" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI189" s="3" t="n">
         <v>46004.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N60" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="M61" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N61" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M62" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N62" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N70" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,16 +8796,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.07</v>
+        <v>4.05</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N72" t="n">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,55 +9227,55 @@
         </is>
       </c>
       <c r="L74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
         <v>1.8</v>
       </c>
-      <c r="M74" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N74" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB74" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N92" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7</v>
+        <v>3.95</v>
       </c>
       <c r="M97" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>1.83</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N99" t="n">
-        <v>1.82</v>
+        <v>5.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="M100" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N104" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="M109" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N109" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB109" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="M110" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="M116" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="N116" t="n">
-        <v>3.44</v>
+        <v>2.08</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="M117" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="N117" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M120" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N120" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,55 +15177,55 @@
         </is>
       </c>
       <c r="L124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB124" t="n">
         <v>1.75</v>
-      </c>
-      <c r="M124" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N124" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="M164" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="N164" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,16 +19982,16 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD164" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="M166" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N166" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="M168" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N168" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="M171" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N171" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21291,10 +21291,10 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB175" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="M178" t="n">
-        <v>3.05</v>
+        <v>6.7</v>
       </c>
       <c r="N178" t="n">
-        <v>2.95</v>
+        <v>16</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="M186" t="n">
         <v>3.75</v>
       </c>
       <c r="N186" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="AC186" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD186" t="n">
         <v>1.62</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
         <v>2.18</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M62" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N65" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,14 +8275,14 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N66" t="n">
         <v>2.2</v>
       </c>
-      <c r="M66" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.75</v>
+        <v>4.15</v>
       </c>
       <c r="M67" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N69" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="N70" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,16 +8796,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="M71" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N71" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4.05</v>
+        <v>1.98</v>
       </c>
       <c r="M72" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M74" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="N74" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,16 +9272,16 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="M77" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="M81" t="n">
         <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M82" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N82" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.15</v>
+        <v>2.5</v>
       </c>
       <c r="M83" t="n">
         <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M85" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB85" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,55 +10774,55 @@
         </is>
       </c>
       <c r="L87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
         <v>2.08</v>
       </c>
-      <c r="M87" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N87" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB87" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,55 +11012,55 @@
         </is>
       </c>
       <c r="L89" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
         <v>1.8</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N89" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB89" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,55 +11369,55 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N92" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
         <v>1.8</v>
       </c>
-      <c r="M92" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N92" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB92" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,55 +11488,55 @@
         </is>
       </c>
       <c r="L93" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N93" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB93" t="n">
         <v>1.95</v>
-      </c>
-      <c r="M93" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N93" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="M97" t="n">
         <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="M99" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M101" t="n">
         <v>3.3</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="M102" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="M106" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N106" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M107" t="n">
         <v>3.3</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N110" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M111" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N111" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.19</v>
+        <v>4.4</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N115" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="M116" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="M126" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="M146" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N146" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="M154" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N154" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19750,10 +19750,10 @@
         <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19988,10 +19988,10 @@
         <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M166" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N166" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="M170" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N170" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="M173" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="N173" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="M174" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N174" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,16 +21172,16 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC174" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="M175" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N175" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,16 +21291,16 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M176" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N176" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M177" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N177" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="M178" t="n">
-        <v>6.7</v>
+        <v>3.05</v>
       </c>
       <c r="N178" t="n">
-        <v>16</v>
+        <v>2.95</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="M183" t="n">
-        <v>3.05</v>
+        <v>6.7</v>
       </c>
       <c r="N183" t="n">
-        <v>2.95</v>
+        <v>16</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
         <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M62" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="M65" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N65" t="n">
-        <v>3.95</v>
+        <v>2.07</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.95</v>
+        <v>1.45</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.15</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N67" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,16 +8439,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="M69" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N70" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB71" t="n">
         <v>1.72</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>2</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="M72" t="n">
         <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="M74" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,16 +9272,16 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,14 +9465,14 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="M76" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N76" t="n">
         <v>3.4</v>
       </c>
-      <c r="N76" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="M77" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB78" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.95</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="M82" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N82" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N83" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.05</v>
+        <v>1.55</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N84" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M85" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N85" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N88" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="M89" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="M90" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB90" t="n">
         <v>1.72</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>2</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.95</v>
+        <v>1.8</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N94" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.4</v>
+        <v>4.15</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M97" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N101" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M105" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N105" t="n">
-        <v>2.35</v>
+        <v>4.15</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N106" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.45</v>
+        <v>4.05</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N107" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="M109" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N109" t="n">
-        <v>2.07</v>
+        <v>3.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.57</v>
+        <v>3.95</v>
       </c>
       <c r="M110" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB110" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="M118" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="M119" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N119" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="M146" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N146" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="M154" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N154" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19750,10 +19750,10 @@
         <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.55</v>
+        <v>11</v>
       </c>
       <c r="M165" t="n">
-        <v>3.25</v>
+        <v>6.7</v>
       </c>
       <c r="N165" t="n">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="M167" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N167" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="M168" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N168" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="M170" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="N170" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="M171" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N171" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="M173" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="N173" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="M174" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N174" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,16 +21172,16 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="M175" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N175" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,16 +21291,16 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB175" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC175" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M178" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N178" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="M179" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N179" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,14 +3753,14 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N28" t="n">
         <v>2.45</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.46</v>
+        <v>1.64</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC60" t="n">
         <v>2.3</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="M62" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N62" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M65" t="n">
         <v>3.35</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N65" t="n">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="M66" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>7.3</v>
+        <v>3.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="M67" t="n">
-        <v>4.05</v>
+        <v>3.67</v>
       </c>
       <c r="N67" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,16 +8439,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>2.35</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="M71" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB71" t="n">
         <v>2</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.72</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M72" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.5</v>
+        <v>4.15</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N80" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="M82" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="M83" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N83" t="n">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="M84" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>5.9</v>
+        <v>2.07</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="M85" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N85" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N87" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB87" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,14 +10893,14 @@
         </is>
       </c>
       <c r="L88" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M88" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N88" t="n">
         <v>2.55</v>
       </c>
-      <c r="M88" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N88" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,10 +11131,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
         <v>2.35</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="M91" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N93" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="M94" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,16 +11771,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.15</v>
+        <v>1.45</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N96" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N97" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N99" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M100" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N103" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M104" t="n">
         <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="M106" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.05</v>
+        <v>1.8</v>
       </c>
       <c r="M107" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N107" t="n">
-        <v>1.8</v>
+        <v>3.95</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="M110" t="n">
         <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="M117" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N117" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="M118" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="N118" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14633,10 +14633,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.55</v>
+        <v>3.75</v>
       </c>
       <c r="M120" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M125" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N125" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18322,10 +18322,10 @@
         <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD150" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE150" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.55</v>
+        <v>11</v>
       </c>
       <c r="M163" t="n">
-        <v>3.25</v>
+        <v>6.7</v>
       </c>
       <c r="N163" t="n">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,16 +19863,16 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD163" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>11</v>
+        <v>2.55</v>
       </c>
       <c r="M165" t="n">
-        <v>6.7</v>
+        <v>3.25</v>
       </c>
       <c r="N165" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20107,10 +20107,10 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.11</v>
+        <v>2.37</v>
       </c>
       <c r="M170" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="N170" t="n">
-        <v>20</v>
+        <v>2.9</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="M173" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="N173" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="M180" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N180" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -1305,10 +1305,10 @@
         <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="M52" t="n">
         <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="M62" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="N62" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB62" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC62" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC62" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD62" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,14 +8156,14 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N65" t="n">
         <v>2.2</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="M67" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,16 +8439,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB71" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.95</v>
+        <v>1.45</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N75" t="n">
-        <v>1.83</v>
+        <v>6.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="M76" t="n">
         <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.15</v>
+        <v>1.83</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="N79" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,55 +9941,55 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB80" t="n">
         <v>1.75</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N80" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="M83" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>7.3</v>
+        <v>2.07</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N84" t="n">
-        <v>2.07</v>
+        <v>2.85</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="M85" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>5.9</v>
+        <v>2.35</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N86" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.05</v>
+        <v>2.2</v>
       </c>
       <c r="M87" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N87" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N90" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N92" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="M95" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,16 +11771,16 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="AC95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="M98" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="N98" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD98" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="M99" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>5.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB99" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1.95</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N100" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N102" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N103" t="n">
-        <v>2.85</v>
+        <v>7.3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="M104" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.8</v>
+        <v>3.95</v>
       </c>
       <c r="M107" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N107" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="M108" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.75</v>
+        <v>4.05</v>
       </c>
       <c r="M111" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N111" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.19</v>
+        <v>3.75</v>
       </c>
       <c r="M115" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N115" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="M118" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="M120" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N120" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14752,10 +14752,10 @@
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,55 +15296,55 @@
         </is>
       </c>
       <c r="L125" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
         <v>1.75</v>
       </c>
-      <c r="M125" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AB125" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>11</v>
+        <v>2.55</v>
       </c>
       <c r="M163" t="n">
-        <v>6.7</v>
+        <v>3.25</v>
       </c>
       <c r="N163" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,16 +19863,16 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE163" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.55</v>
+        <v>11</v>
       </c>
       <c r="M165" t="n">
-        <v>3.25</v>
+        <v>6.7</v>
       </c>
       <c r="N165" t="n">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,16 +20101,16 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC165" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD165" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE165" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.37</v>
+        <v>1.11</v>
       </c>
       <c r="M170" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="N170" t="n">
-        <v>2.9</v>
+        <v>20</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.83</v>
+        <v>2.37</v>
       </c>
       <c r="M171" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N171" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="M173" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="N173" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M176" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N176" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M177" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N177" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="M180" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N180" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.19</v>
+        <v>2.4</v>
       </c>
       <c r="M181" t="n">
-        <v>6.7</v>
+        <v>3.05</v>
       </c>
       <c r="N181" t="n">
-        <v>16</v>
+        <v>2.95</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.61</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.75</v>
+        <v>2.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.46</v>
+        <v>1.64</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,16 +7725,16 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N65" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,16 +8558,16 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="M69" t="n">
         <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M72" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,55 +9108,55 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
         <v>1.85</v>
       </c>
-      <c r="M73" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N73" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="M74" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N74" t="n">
-        <v>3.95</v>
+        <v>7.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N76" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.2</v>
+        <v>4.05</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="M79" t="n">
-        <v>3.67</v>
+        <v>4.3</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M80" t="n">
         <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="M84" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N84" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="M85" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N86" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10703,7 +10703,7 @@
         <v>1.85</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="M87" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>2.8</v>
+        <v>2.07</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="M91" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.15</v>
+        <v>1.55</v>
       </c>
       <c r="M92" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N92" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="M98" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>2.35</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="M99" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N99" t="n">
-        <v>5.9</v>
+        <v>2.95</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB99" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="M100" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>5.4</v>
+        <v>2.55</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12369,7 +12369,7 @@
         <v>1.85</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N106" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="M107" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="N107" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,16 +13199,16 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,55 +13273,55 @@
         </is>
       </c>
       <c r="L108" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
         <v>1.92</v>
       </c>
-      <c r="M108" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N108" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB108" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N110" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N115" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="M116" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14752,10 +14752,10 @@
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N130" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18322,10 +18322,10 @@
         <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD150" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18560,10 +18560,10 @@
         <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD152" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="M171" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N171" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="M176" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N176" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M177" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="N177" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.19</v>
+        <v>2.1</v>
       </c>
       <c r="M179" t="n">
-        <v>6.7</v>
+        <v>3.65</v>
       </c>
       <c r="N179" t="n">
-        <v>16</v>
+        <v>3.3</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB179" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4.2</v>
+        <v>1.19</v>
       </c>
       <c r="M180" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="N180" t="n">
-        <v>1.84</v>
+        <v>16</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB180" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>

--- a/jogos_2025-12-13.xlsx
+++ b/jogos_2025-12-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c